--- a/data/dividends_info_20260728.xlsx
+++ b/data/dividends_info_20260728.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>45.34000015258789</v>
+        <v>44.47499847412109</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1985002198877651</v>
+        <v>0.2023608838398697</v>
       </c>
       <c r="J2" t="n">
         <v>230</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>65.5</v>
+        <v>65.05000305175781</v>
       </c>
       <c r="I3" t="n">
-        <v>1.068702290076336</v>
+        <v>1.076095260815033</v>
       </c>
       <c r="J3" t="n">
         <v>209</v>
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>8.979999542236328</v>
+        <v>9.180000305175781</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6681514817210997</v>
+        <v>0.6535947495140209</v>
       </c>
       <c r="J4" t="n">
         <v>139</v>
@@ -664,10 +664,10 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.4600000083446503</v>
+        <v>0.4740000069141388</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8695652016169185</v>
+        <v>0.8438818442305566</v>
       </c>
       <c r="J5" t="n">
         <v>139</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>45.34000015258789</v>
+        <v>44.47499847412109</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1985002198877651</v>
+        <v>0.2023608838398697</v>
       </c>
       <c r="J6" t="n">
         <v>139</v>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>22.25</v>
+        <v>22.01499938964844</v>
       </c>
       <c r="I8" t="n">
-        <v>1.213483146067416</v>
+        <v>1.226436554556324</v>
       </c>
       <c r="J8" t="n">
         <v>118</v>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>6.039999961853027</v>
+        <v>6</v>
       </c>
       <c r="I9" t="n">
-        <v>3.311258299058689</v>
+        <v>3.333333333333333</v>
       </c>
       <c r="J9" t="n">
         <v>111</v>
@@ -899,10 +899,10 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>7.75</v>
+        <v>7.699999809265137</v>
       </c>
       <c r="I10" t="n">
-        <v>0.7741935483870968</v>
+        <v>0.7792207985226717</v>
       </c>
       <c r="J10" t="n">
         <v>83</v>
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0.4600000083446503</v>
+        <v>0.4740000069141388</v>
       </c>
       <c r="I11" t="n">
-        <v>0.8695652016169185</v>
+        <v>0.8438818442305566</v>
       </c>
       <c r="J11" t="n">
         <v>83</v>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>5</v>
+        <v>5.039999961853027</v>
       </c>
       <c r="I13" t="n">
-        <v>0.76</v>
+        <v>0.753968259674922</v>
       </c>
       <c r="J13" t="n">
         <v>62</v>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>22.25</v>
+        <v>22.01499938964844</v>
       </c>
       <c r="I14" t="n">
-        <v>1.213483146067416</v>
+        <v>1.226436554556324</v>
       </c>
       <c r="J14" t="n">
         <v>55</v>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>45.34000015258789</v>
+        <v>44.47499847412109</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1985002198877651</v>
+        <v>0.2023608838398697</v>
       </c>
       <c r="J15" t="n">
         <v>55</v>
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>92.75</v>
+        <v>93.75</v>
       </c>
       <c r="I16" t="n">
-        <v>1.433962264150943</v>
+        <v>1.418666666666667</v>
       </c>
       <c r="J16" t="n">
         <v>55</v>
@@ -1228,10 +1228,10 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>5.760000228881836</v>
+        <v>5.71999979019165</v>
       </c>
       <c r="I17" t="n">
-        <v>5.208333126372769</v>
+        <v>5.244755437131728</v>
       </c>
       <c r="J17" t="n">
         <v>48</v>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>0.4600000083446503</v>
+        <v>0.4740000069141388</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8695652016169185</v>
+        <v>0.8438818442305566</v>
       </c>
       <c r="J18" t="n">
         <v>27</v>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>2.700000047683716</v>
+        <v>2.900000095367432</v>
       </c>
       <c r="I19" t="n">
-        <v>8.148148004246677</v>
+        <v>7.586206647076882</v>
       </c>
       <c r="J19" t="n">
         <v>13</v>
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>5</v>
+        <v>5.039999961853027</v>
       </c>
       <c r="I20" t="n">
-        <v>0.76</v>
+        <v>0.753968259674922</v>
       </c>
       <c r="J20" t="n">
         <v>6</v>
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>2.970000028610229</v>
+        <v>2.980000019073486</v>
       </c>
       <c r="I22" t="n">
-        <v>4.98212116412807</v>
+        <v>4.965402652782704</v>
       </c>
       <c r="J22" t="n">
         <v>6</v>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>5.769999980926514</v>
+        <v>5.639999866485596</v>
       </c>
       <c r="I23" t="n">
-        <v>4.33275564690481</v>
+        <v>4.432624218407656</v>
       </c>
       <c r="J23" t="n">
         <v>-1</v>
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>3.950000047683716</v>
+        <v>3.990000009536743</v>
       </c>
       <c r="I24" t="n">
-        <v>3.544303754682133</v>
+        <v>3.508771921438032</v>
       </c>
       <c r="J24" t="n">
         <v>-8</v>
@@ -1604,10 +1604,10 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>9.977999687194824</v>
+        <v>9.869999885559082</v>
       </c>
       <c r="I25" t="n">
-        <v>2.605732693434223</v>
+        <v>2.634245217980288</v>
       </c>
       <c r="J25" t="n">
         <v>-8</v>
@@ -1651,10 +1651,10 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>13.38000011444092</v>
+        <v>13.30000019073486</v>
       </c>
       <c r="I26" t="n">
-        <v>4.48430489438057</v>
+        <v>4.51127813079263</v>
       </c>
       <c r="J26" t="n">
         <v>-8</v>
@@ -1698,10 +1698,10 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>2.644000053405762</v>
+        <v>2.650000095367432</v>
       </c>
       <c r="I27" t="n">
-        <v>8.320726004396857</v>
+        <v>8.301886493686947</v>
       </c>
       <c r="J27" t="n">
         <v>-8</v>
@@ -1745,10 +1745,10 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>0.4600000083446503</v>
+        <v>0.4740000069141388</v>
       </c>
       <c r="I28" t="n">
-        <v>0.8695652016169185</v>
+        <v>0.8438818442305566</v>
       </c>
       <c r="J28" t="n">
         <v>-8</v>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>6.434999942779541</v>
+        <v>6.494999885559082</v>
       </c>
       <c r="I29" t="n">
-        <v>3.729603762767621</v>
+        <v>3.695150180581429</v>
       </c>
       <c r="J29" t="n">
         <v>-8</v>
@@ -1839,10 +1839,10 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>18.70000076293945</v>
+        <v>19.04999923706055</v>
       </c>
       <c r="I30" t="n">
-        <v>2.010695105131624</v>
+        <v>1.973753359887365</v>
       </c>
       <c r="J30" t="n">
         <v>-8</v>
@@ -1933,10 +1933,10 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>5.690000057220459</v>
+        <v>5.679999828338623</v>
       </c>
       <c r="I32" t="n">
-        <v>2.108963071937463</v>
+        <v>2.112676120187481</v>
       </c>
       <c r="J32" t="n">
         <v>-15</v>
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>4.400000095367432</v>
+        <v>4.230000019073486</v>
       </c>
       <c r="I36" t="n">
-        <v>1.590909056427066</v>
+        <v>1.654846328235535</v>
       </c>
       <c r="J36" t="n">
         <v>-22</v>
@@ -2168,10 +2168,10 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>33.70000076293945</v>
+        <v>34.25</v>
       </c>
       <c r="I37" t="n">
-        <v>0.4451038474899914</v>
+        <v>0.437956204379562</v>
       </c>
       <c r="J37" t="n">
         <v>-22</v>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>5.25</v>
+        <v>5.300000190734863</v>
       </c>
       <c r="I39" t="n">
-        <v>0.7619047619047619</v>
+        <v>0.7547169539715406</v>
       </c>
       <c r="J39" t="n">
         <v>-29</v>
@@ -3668,7 +3668,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>A2A S.p.A.</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3678,14 +3678,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A2A S.p.A.</t>
+          <t>AEDES S.p.A.</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3702,7 +3702,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>AEDES S.p.A.</t>
+          <t>AMPLIFON S.p.A.</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3712,7 +3712,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -3729,14 +3729,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>AMPLIFON S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3763,14 +3763,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3940,7 +3940,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>ESAUTOMOTION S.p.A.</t>
+          <t>Ferrari N.V.</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3950,14 +3950,14 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>ESAUTOMOTION S.p.A.</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3967,7 +3967,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
@@ -3984,7 +3984,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -4008,7 +4008,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Ferrari N.V.</t>
+          <t>DEA CAPITAL REAL ESTATE SGR S.p.A.</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -4018,14 +4018,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4035,14 +4035,14 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>DEA CAPITAL REAL ESTATE SGR S.p.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -4059,7 +4059,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4086,14 +4086,14 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -4103,14 +4103,14 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
+          <t>CALTAGIRONE S.p.A.</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -4120,14 +4120,14 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>CALTAGIRONE S.p.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -4137,14 +4137,14 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>CIR S.p.A. - COMPAGNIE INDUSTRIALI RIUNITE</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -4154,14 +4154,14 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Comer Industries S.p.A.</t>
+          <t>Svas Biosana S.p.A.</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -4171,14 +4171,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>DiaSorin S.p.A</t>
+          <t>The Italian Sea Group S.p.A.</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -4188,14 +4188,14 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>Tinexta S.p.A.</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -4212,7 +4212,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>VINCENZO ZUCCHI S.p.A.</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -4222,14 +4222,14 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Ferretti S.p.A.</t>
+          <t>VNE S.p.A.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -4239,14 +4239,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>VINCENZO ZUCCHI S.p.A.</t>
+          <t>CAIRO COMMUNICATION S.p.A.</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -4256,14 +4256,14 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Misitano &amp; Stracuzzi S.p.A.</t>
+          <t>Ferretti S.p.A.</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -4273,14 +4273,14 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Nusco S.p.A.</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -4297,7 +4297,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Svas Biosana S.p.A.</t>
+          <t>Comer Industries S.p.A.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -4307,14 +4307,14 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>The Italian Sea Group S.p.A.</t>
+          <t>DiaSorin S.p.A</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -4324,14 +4324,14 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Tinexta S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -4348,7 +4348,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>CAIRO COMMUNICATION S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -4365,7 +4365,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>VNE S.p.A.</t>
+          <t>GREEN OLEO S.p.A</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -4375,14 +4375,14 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>GREEN OLEO S.p.A</t>
+          <t>CIR S.p.A. - COMPAGNIE INDUSTRIALI RIUNITE</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -4392,14 +4392,14 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>Misitano &amp; Stracuzzi S.p.A.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -4409,14 +4409,14 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>Nusco S.p.A.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -4426,14 +4426,14 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>BIESSE S.p.A.</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -4450,7 +4450,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>BIESSE S.p.A.</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -4467,7 +4467,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>CLABO S.p.A.</t>
+          <t>SALVATORE FERRAGAMO S.p.A.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -4477,14 +4477,14 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>SALVATORE FERRAGAMO S.p.A.</t>
+          <t>ENAV S.p.A.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -4501,7 +4501,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>SALVATORE FERRAGAMO S.p.A.</t>
+          <t>EuroGroup Laminations S.p.A.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -4511,14 +4511,14 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>EuroGroup Laminations S.p.A.</t>
+          <t>SALVATORE FERRAGAMO S.p.A.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -4535,7 +4535,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>ENAV S.p.A.</t>
+          <t>CLABO S.p.A.</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -4545,7 +4545,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -4586,7 +4586,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -4603,7 +4603,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>IGD SIIQ S.p.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -4620,7 +4620,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -4630,14 +4630,14 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>CREDITO EMILIANO S.p.A.</t>
+          <t>BUZZI S.p.A.</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -4654,7 +4654,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>CAREL INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -4664,14 +4664,14 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>SAFILO GROUP S.p.A.</t>
+          <t>CREDITO EMILIANO S.p.A.</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -4688,7 +4688,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>SAFILO GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -4705,7 +4705,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>IGD SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -4715,14 +4715,14 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -4732,14 +4732,14 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -4749,14 +4749,14 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>BUZZI S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -4773,7 +4773,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>CAREL INDUSTRIES S.p.A.</t>
+          <t>DATALOGIC S.p.A.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -4790,7 +4790,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -4807,7 +4807,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>DATALOGIC S.p.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -4817,14 +4817,14 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>TESMEC S.p.A.</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -4834,14 +4834,14 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>doValue S.p.A.</t>
+          <t>TESMEC S.p.A.</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -4858,7 +4858,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>TREVI - Finanziaria Industriale S.p.A.</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -4875,7 +4875,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>BFF Bank S.P.A.</t>
+          <t>Technoprobe S.p.A.</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -4885,14 +4885,14 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Banco BPM S.p.A.</t>
+          <t>Technoprobe S.p.A.</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -4909,7 +4909,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Technoprobe S.p.A.</t>
+          <t>doValue S.p.A.</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -4926,7 +4926,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Technoprobe S.p.A.</t>
+          <t>BFF Bank S.P.A.</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -4936,14 +4936,14 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>SIT S.p.A.</t>
+          <t>Banco BPM S.p.A.</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -4953,14 +4953,14 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>TESMEC S.p.A.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -4970,14 +4970,14 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>TESMEC S.p.A.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -4987,14 +4987,14 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>PIQUADRO S.p.A.</t>
+          <t>Bper Banca S.P.A.</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -5004,7 +5004,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -5021,14 +5021,14 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>SIT S.p.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -5038,7 +5038,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -5055,14 +5055,14 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>PIQUADRO S.p.A.</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -5072,14 +5072,14 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>INTERPUMP GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -5113,7 +5113,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>INTERPUMP GROUP S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -5130,7 +5130,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>TREVI - Finanziaria Industriale S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -5147,7 +5147,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Bper Banca S.P.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -5157,14 +5157,14 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>GEFRAN S.p.A.</t>
+          <t>Unipol S.p.A.</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -5181,7 +5181,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>F.I.L.A. S.p.A.</t>
+          <t>doValue S.p.A.</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -5191,14 +5191,14 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -5208,14 +5208,14 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Bper Banca S.P.A.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -5225,14 +5225,14 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -5242,14 +5242,14 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>BANCA SISTEMA S.p.A.</t>
+          <t>OPS Retail S.p.A.</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -5259,14 +5259,14 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Abitare In S.p.A.</t>
+          <t>PROMOTICA S.p.A.</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -5276,14 +5276,14 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>BANCA SISTEMA S.p.A.</t>
+          <t>TXT E-SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -5293,14 +5293,14 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>GVS S.p.A.</t>
+          <t>REVO Insurance S.p.A.</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -5317,7 +5317,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>BANCA SISTEMA S.p.A.</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -5327,14 +5327,14 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
+          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -5351,7 +5351,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>PROMOTICA S.p.A.</t>
+          <t>GVS S.p.A.</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -5361,14 +5361,14 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>doValue S.p.A.</t>
+          <t>GEFRAN S.p.A.</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -5378,14 +5378,14 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Unipol S.p.A.</t>
+          <t>F.I.L.A. S.p.A.</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -5402,7 +5402,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>TXT E-SOLUTIONS S.p.A.</t>
+          <t>Bper Banca S.P.A.</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -5412,14 +5412,14 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>OPS Retail S.p.A.</t>
+          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -5429,14 +5429,14 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>BANCA SISTEMA S.p.A.</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -5446,14 +5446,14 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>Abitare In S.p.A.</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -5463,14 +5463,14 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>REVO Insurance S.p.A.</t>
+          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -5648,104 +5648,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>stock_name</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>ticker</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>detachment_date</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>payment_date</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>last_close</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>dividend</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>currency</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>ratio</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>miss_days</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>is_opportunity</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>MEDIOLANUM GESTIONE FONDI SGR p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>IT0003922249</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2026-08-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>1.043799996376038</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.15403</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>14.75665841490475</v>
-      </c>
-      <c r="I2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5756,129 +5661,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Aquafil S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Half Year Preliminary Results</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Sesa S.p.A.</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>VINCENZO ZUCCHI S.p.A.</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>eVISO S.p.A.</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Annual Preliminary Results</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>